--- a/frontend/public/exemple inventaire.xlsx
+++ b/frontend/public/exemple inventaire.xlsx
@@ -6449,172 +6449,98 @@
       <c r="R45" s="56"/>
     </row>
     <row r="46" spans="2:18" s="24" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B46" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="C46" s="58" t="s">
-        <v>24</v>
-      </c>
-      <c r="D46" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="E46" s="73">
-        <v>25</v>
-      </c>
+      <c r="B46" s="57"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="73"/>
       <c r="F46" s="61"/>
       <c r="G46" s="67"/>
       <c r="H46" s="67"/>
-      <c r="I46" s="64">
-        <v>0</v>
-      </c>
+      <c r="I46" s="64"/>
       <c r="J46" s="65">
         <f>I46</f>
-        <v>0</v>
-      </c>
-      <c r="K46" s="68" t="s">
-        <v>100</v>
-      </c>
+      </c>
+      <c r="K46" s="68"/>
       <c r="L46" s="51"/>
       <c r="M46" s="52">
         <f t="shared" si="1"/>
-        <v>0</v>
       </c>
       <c r="N46" s="53"/>
-      <c r="O46" s="54">
-        <v>5410033853002</v>
-      </c>
+      <c r="O46" s="54"/>
       <c r="P46" s="55">
         <f>I46+G46*E46</f>
-        <v>0</v>
       </c>
       <c r="R46" s="56"/>
     </row>
     <row r="47" spans="2:18" s="24" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="C47" s="58" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47" s="59" t="s">
-        <v>112</v>
-      </c>
-      <c r="E47" s="60">
-        <v>12</v>
-      </c>
+      <c r="B47" s="57"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="60"/>
       <c r="F47" s="61"/>
-      <c r="G47" s="62">
-        <v>0</v>
-      </c>
+      <c r="G47" s="62"/>
       <c r="H47" s="67"/>
-      <c r="I47" s="64">
-        <v>0</v>
-      </c>
+      <c r="I47" s="64"/>
       <c r="J47" s="65">
         <f>G47+I47/E47</f>
-        <v>0</v>
-      </c>
-      <c r="K47" s="68" t="s">
-        <v>113</v>
-      </c>
+      </c>
+      <c r="K47" s="68"/>
       <c r="L47" s="51"/>
       <c r="M47" s="52">
         <f t="shared" si="1"/>
-        <v>0</v>
       </c>
       <c r="N47" s="53"/>
-      <c r="O47" s="54">
-        <v>4033854001301</v>
-      </c>
+      <c r="O47" s="54"/>
       <c r="P47" s="55">
         <f t="shared" si="7"/>
-        <v>0</v>
       </c>
       <c r="R47" s="56"/>
     </row>
     <row r="48" spans="2:18" s="24" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="C48" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="D48" s="69" t="s">
-        <v>114</v>
-      </c>
-      <c r="E48" s="70">
-        <v>12</v>
-      </c>
+      <c r="B48" s="41"/>
+      <c r="C48" s="42"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="70"/>
       <c r="F48" s="71"/>
-      <c r="G48" s="62">
-        <v>0</v>
-      </c>
+      <c r="G48" s="62"/>
       <c r="H48" s="67"/>
-      <c r="I48" s="64">
-        <v>0</v>
-      </c>
+      <c r="I48" s="64"/>
       <c r="J48" s="49">
         <f>G48+I48/E48</f>
-        <v>0</v>
-      </c>
-      <c r="K48" s="68" t="s">
-        <v>113</v>
-      </c>
+      </c>
+      <c r="K48" s="68"/>
       <c r="L48" s="51"/>
       <c r="M48" s="52">
         <f t="shared" si="1"/>
-        <v>0</v>
       </c>
       <c r="N48" s="53"/>
-      <c r="O48" s="54" t="s">
-        <v>115</v>
-      </c>
+      <c r="O48" s="54"/>
       <c r="P48" s="55">
         <f t="shared" si="7"/>
-        <v>0</v>
       </c>
       <c r="R48" s="56"/>
     </row>
     <row r="49" spans="2:19" s="24" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="C49" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49" s="69" t="s">
-        <v>116</v>
-      </c>
-      <c r="E49" s="70">
-        <v>6</v>
-      </c>
+      <c r="B49" s="41"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="70"/>
       <c r="F49" s="71"/>
-      <c r="G49" s="62">
-        <v>0</v>
-      </c>
+      <c r="G49" s="62"/>
       <c r="H49" s="67"/>
-      <c r="I49" s="64">
-        <v>0</v>
-      </c>
+      <c r="I49" s="64"/>
       <c r="J49" s="49">
         <f>G49+I49/E49</f>
-        <v>0</v>
-      </c>
-      <c r="K49" s="68" t="s">
-        <v>117</v>
-      </c>
+      </c>
+      <c r="K49" s="68"/>
       <c r="L49" s="51"/>
       <c r="M49" s="52">
         <f t="shared" si="1"/>
-        <v>0</v>
       </c>
       <c r="N49" s="53"/>
-      <c r="O49" s="54" t="s">
-        <v>118</v>
-      </c>
+      <c r="O49" s="54"/>
       <c r="P49" s="55">
         <f>I49+G49*E49</f>
-        <v>0</v>
       </c>
       <c r="R49" s="56"/>
     </row>
